--- a/rsvp_forms/045_wedding_reception_invitation_form--rsvp_forms.xlsx
+++ b/rsvp_forms/045_wedding_reception_invitation_form--rsvp_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1232,29 +1232,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>vegetarian</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Vegetarian</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>meal_preferences_choices</t>
+          <t>attending_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>attending</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Attending</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>attending</t>
+          <t>declining</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Attending</t>
+          <t>Declining</t>
         </is>
       </c>
     </row>
@@ -1283,29 +1283,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>declining</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Declining</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>attending_choices</t>
+          <t>meal_attendance_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>maybe</t>
+          <t>beef</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Beef</t>
         </is>
       </c>
     </row>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>beef</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Beef</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -1334,29 +1334,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>vegetarian</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vegetarian</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>meal_attendance_choices</t>
+          <t>dressing_code_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>both</t>
+          <t>formal</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Formal</t>
         </is>
       </c>
     </row>
@@ -1368,29 +1368,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>formal</t>
+          <t>casual</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Formal</t>
+          <t>Casual</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dressing_code_choices</t>
+          <t>transportation_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>casual</t>
+          <t>by_car</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Casual</t>
+          <t>By car</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>by_car</t>
+          <t>by_bus</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>By car</t>
+          <t>By bus</t>
         </is>
       </c>
     </row>
@@ -1419,29 +1419,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>by_bus</t>
+          <t>by_train</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>By bus</t>
+          <t>By train</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>transportation_choices</t>
+          <t>accommodations_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>by_train</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>By train</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>motel</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>Motel</t>
         </is>
       </c>
     </row>
@@ -1470,27 +1470,10 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>motel</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
-        <is>
-          <t>Motel</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>accommodations_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
         <is>
           <t>None</t>
         </is>
